--- a/artfynd/A 56424-2024 artfynd.xlsx
+++ b/artfynd/A 56424-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747589</v>
+        <v>122747590</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635214</v>
+        <v>635269</v>
       </c>
       <c r="R2" t="n">
-        <v>7051463</v>
+        <v>7051686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747590</v>
+        <v>122747589</v>
       </c>
       <c r="B3" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635269</v>
+        <v>635214</v>
       </c>
       <c r="R3" t="n">
-        <v>7051686</v>
+        <v>7051463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56424-2024 artfynd.xlsx
+++ b/artfynd/A 56424-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747590</v>
+        <v>122747589</v>
       </c>
       <c r="B2" t="n">
         <v>78502</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635269</v>
+        <v>635214</v>
       </c>
       <c r="R2" t="n">
-        <v>7051686</v>
+        <v>7051463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747589</v>
+        <v>122747590</v>
       </c>
       <c r="B3" t="n">
         <v>78502</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635214</v>
+        <v>635269</v>
       </c>
       <c r="R3" t="n">
-        <v>7051463</v>
+        <v>7051686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56424-2024 artfynd.xlsx
+++ b/artfynd/A 56424-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747589</v>
+        <v>122747590</v>
       </c>
       <c r="B2" t="n">
         <v>78502</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635214</v>
+        <v>635269</v>
       </c>
       <c r="R2" t="n">
-        <v>7051463</v>
+        <v>7051686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747590</v>
+        <v>122747589</v>
       </c>
       <c r="B3" t="n">
         <v>78502</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635269</v>
+        <v>635214</v>
       </c>
       <c r="R3" t="n">
-        <v>7051686</v>
+        <v>7051463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56424-2024 artfynd.xlsx
+++ b/artfynd/A 56424-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747590</v>
+        <v>122747589</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635269</v>
+        <v>635214</v>
       </c>
       <c r="R2" t="n">
-        <v>7051686</v>
+        <v>7051463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747589</v>
+        <v>122747590</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635214</v>
+        <v>635269</v>
       </c>
       <c r="R3" t="n">
-        <v>7051463</v>
+        <v>7051686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56424-2024 artfynd.xlsx
+++ b/artfynd/A 56424-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747589</v>
       </c>
       <c r="B2" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747590</v>
       </c>
       <c r="B3" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
